--- a/SubRES_TMPL/SubRES_NewTechs_02B_TRA_No_ELC.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs_02B_TRA_No_ELC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\My Drive\001_Academic\002_Course_Works\003_2026_Sping_Semester\003_Low-Carbon Technologies and Policies\000_ICP_BL\006_Cambodia_TIMES_Model_V002\KHM_TIMES_V002_20260604\SubRES_TMPL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261015\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B9B577-6DF0-4ABC-B0B8-EADCFB0CD0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19DD8E07-3E8F-47AE-9685-209639DEA126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TRA" sheetId="5" r:id="rId1"/>
@@ -23,6 +23,19 @@
     <definedName name="FID_1">[1]AGR_Fuels!$A$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -762,7 +775,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="122">
   <si>
     <t>~FI_T</t>
   </si>
@@ -1119,6 +1132,15 @@
   </si>
   <si>
     <t>Demand Technologies Transport Sector - New Motor - Kerosenes</t>
+  </si>
+  <si>
+    <t>TCANELC1</t>
+  </si>
+  <si>
+    <t>Demand Technologies Transport Sector - New Cars - Electricity</t>
+  </si>
+  <si>
+    <t>TRAELC</t>
   </si>
 </sst>
 </file>
@@ -1679,13 +1701,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>829022</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>47279</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>390701</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>61133</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2527,34 +2549,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="B1:V24"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:V25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11" customWidth="1"/>
     <col min="13" max="13" width="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.33203125" customWidth="1"/>
-    <col min="15" max="15" width="7.109375" customWidth="1"/>
-    <col min="16" max="16" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="78.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.6640625" customWidth="1"/>
-    <col min="19" max="19" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.28515625" customWidth="1"/>
+    <col min="15" max="15" width="7.140625" customWidth="1"/>
+    <col min="16" max="16" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="78.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.7109375" customWidth="1"/>
+    <col min="19" max="19" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:22" ht="15" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
         <v>40</v>
       </c>
@@ -2578,7 +2600,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="2:22" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:22" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
         <v>63</v>
       </c>
@@ -2613,7 +2635,7 @@
       <c r="U2" s="37"/>
       <c r="V2" s="37"/>
     </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:22" x14ac:dyDescent="0.2">
       <c r="N3" s="38" t="s">
         <v>8</v>
       </c>
@@ -2642,7 +2664,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:22" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:22" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
       <c r="D4" s="19"/>
@@ -2676,7 +2698,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="2:22" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
       <c r="D5" s="19"/>
@@ -2691,7 +2713,7 @@
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.2">
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
@@ -2711,7 +2733,7 @@
       <c r="U8" s="41"/>
       <c r="V8" s="41"/>
     </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B9" s="8" t="s">
         <v>1</v>
       </c>
@@ -2774,7 +2796,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="2:22" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:22" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
         <v>53</v>
       </c>
@@ -2835,7 +2857,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="2:22" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
         <v>58</v>
       </c>
@@ -2876,9 +2898,9 @@
       <c r="U11" s="43"/>
       <c r="V11" s="43"/>
     </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B12" t="str">
-        <f t="shared" ref="B12:B24" si="0">P12</f>
+        <f t="shared" ref="B12:B25" si="0">P12</f>
         <v>TCANDSL1</v>
       </c>
       <c r="C12" t="s">
@@ -2934,13 +2956,13 @@
       </c>
       <c r="V12" s="41"/>
     </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B13" t="str">
-        <f t="shared" si="0"/>
-        <v>TCANLPG1</v>
-      </c>
-      <c r="C13" t="s">
-        <v>75</v>
+        <f t="shared" ref="B13" si="1">P13</f>
+        <v>TCANELC1</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="D13" t="s">
         <v>82</v>
@@ -2949,17 +2971,17 @@
         <v>2022</v>
       </c>
       <c r="F13" s="18">
-        <v>0.39900000000000002</v>
+        <v>0.4</v>
       </c>
       <c r="G13" s="17">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="H13" s="18">
         <v>1.25</v>
       </c>
       <c r="I13" s="26">
-        <f>15.5*1.08</f>
-        <v>16.740000000000002</v>
+        <f>16*1.08</f>
+        <v>17.28</v>
       </c>
       <c r="J13" s="18">
         <v>0.16</v>
@@ -2975,10 +2997,10 @@
       </c>
       <c r="O13" s="41"/>
       <c r="P13" s="37" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="Q13" s="37" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="R13" s="41" t="s">
         <v>95</v>
@@ -2992,40 +3014,40 @@
       </c>
       <c r="V13" s="41"/>
     </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B14" s="27" t="str">
+    <row r="14" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B14" t="str">
         <f t="shared" si="0"/>
-        <v>TCANGSL1</v>
-      </c>
-      <c r="C14" s="27" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" s="27" t="s">
+        <v>TCANLPG1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" t="s">
         <v>82</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14">
         <v>2022</v>
       </c>
-      <c r="F14" s="30">
-        <v>0.42000000000000004</v>
-      </c>
-      <c r="G14" s="32">
-        <v>11.5</v>
-      </c>
-      <c r="H14" s="30">
+      <c r="F14" s="18">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="G14" s="17">
+        <v>14</v>
+      </c>
+      <c r="H14" s="18">
         <v>1.25</v>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="26">
         <f>15.5*1.08</f>
         <v>16.740000000000002</v>
       </c>
-      <c r="J14" s="30">
-        <v>0.15</v>
-      </c>
-      <c r="K14" s="27">
+      <c r="J14" s="18">
+        <v>0.16</v>
+      </c>
+      <c r="K14">
         <v>20</v>
       </c>
-      <c r="L14" s="33">
+      <c r="L14" s="25">
         <v>1E-3</v>
       </c>
       <c r="N14" t="s">
@@ -3033,10 +3055,10 @@
       </c>
       <c r="O14" s="41"/>
       <c r="P14" s="37" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q14" s="37" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R14" s="41" t="s">
         <v>95</v>
@@ -3050,40 +3072,40 @@
       </c>
       <c r="V14" s="41"/>
     </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B15" t="str">
+    <row r="15" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B15" s="27" t="str">
         <f t="shared" si="0"/>
-        <v>TPUNDSL1</v>
-      </c>
-      <c r="C15" t="s">
-        <v>74</v>
-      </c>
-      <c r="D15" t="s">
-        <v>83</v>
-      </c>
-      <c r="E15">
+        <v>TCANGSL1</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" s="27">
         <v>2022</v>
       </c>
-      <c r="F15" s="18">
-        <v>0.1575</v>
-      </c>
-      <c r="G15">
-        <v>50</v>
-      </c>
-      <c r="H15">
-        <v>15</v>
-      </c>
-      <c r="I15" s="26">
-        <f>1.08*24</f>
-        <v>25.92</v>
-      </c>
-      <c r="J15" s="18">
-        <v>0.24</v>
-      </c>
-      <c r="K15">
-        <v>30</v>
-      </c>
-      <c r="L15">
+      <c r="F15" s="30">
+        <v>0.42000000000000004</v>
+      </c>
+      <c r="G15" s="32">
+        <v>11.5</v>
+      </c>
+      <c r="H15" s="30">
+        <v>1.25</v>
+      </c>
+      <c r="I15" s="31">
+        <f>15.5*1.08</f>
+        <v>16.740000000000002</v>
+      </c>
+      <c r="J15" s="30">
+        <v>0.15</v>
+      </c>
+      <c r="K15" s="27">
+        <v>20</v>
+      </c>
+      <c r="L15" s="33">
         <v>1E-3</v>
       </c>
       <c r="N15" t="s">
@@ -3091,10 +3113,10 @@
       </c>
       <c r="O15" s="41"/>
       <c r="P15" s="37" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q15" s="37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R15" s="41" t="s">
         <v>95</v>
@@ -3108,40 +3130,40 @@
       </c>
       <c r="V15" s="41"/>
     </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B16" s="27" t="str">
+    <row r="16" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B16" t="str">
         <f t="shared" si="0"/>
-        <v>TPUNLPG1</v>
-      </c>
-      <c r="C16" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" s="27" t="s">
+        <v>TPUNDSL1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" t="s">
         <v>83</v>
       </c>
-      <c r="E16" s="27">
+      <c r="E16">
         <v>2022</v>
       </c>
-      <c r="F16" s="30">
-        <v>0.10500000000000001</v>
-      </c>
-      <c r="G16" s="27">
+      <c r="F16" s="18">
+        <v>0.1575</v>
+      </c>
+      <c r="G16">
         <v>50</v>
       </c>
-      <c r="H16" s="27">
+      <c r="H16">
         <v>15</v>
       </c>
-      <c r="I16" s="31">
-        <f>1.08*23.25</f>
-        <v>25.110000000000003</v>
-      </c>
-      <c r="J16" s="30">
+      <c r="I16" s="26">
+        <f>1.08*24</f>
+        <v>25.92</v>
+      </c>
+      <c r="J16" s="18">
         <v>0.24</v>
       </c>
-      <c r="K16" s="27">
+      <c r="K16">
         <v>30</v>
       </c>
-      <c r="L16" s="27">
+      <c r="L16">
         <v>1E-3</v>
       </c>
       <c r="N16" t="s">
@@ -3149,10 +3171,10 @@
       </c>
       <c r="O16" s="41"/>
       <c r="P16" s="37" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q16" s="37" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="R16" s="41" t="s">
         <v>95</v>
@@ -3166,438 +3188,496 @@
       </c>
       <c r="V16" s="41"/>
     </row>
-    <row r="17" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B17" s="28" t="str">
+    <row r="17" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B17" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>TPUNLPG1</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" s="27">
+        <v>2022</v>
+      </c>
+      <c r="F17" s="30">
+        <v>0.10500000000000001</v>
+      </c>
+      <c r="G17" s="27">
+        <v>50</v>
+      </c>
+      <c r="H17" s="27">
+        <v>15</v>
+      </c>
+      <c r="I17" s="31">
+        <f>1.08*23.25</f>
+        <v>25.110000000000003</v>
+      </c>
+      <c r="J17" s="30">
+        <v>0.24</v>
+      </c>
+      <c r="K17" s="27">
+        <v>30</v>
+      </c>
+      <c r="L17" s="27">
+        <v>1E-3</v>
+      </c>
+      <c r="N17" t="s">
+        <v>62</v>
+      </c>
+      <c r="O17" s="41"/>
+      <c r="P17" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q17" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="R17" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="S17" s="41" t="s">
+        <v>66</v>
+      </c>
+      <c r="T17" s="41"/>
+      <c r="U17" s="41" t="s">
+        <v>73</v>
+      </c>
+      <c r="V17" s="41"/>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B18" s="28" t="str">
         <f t="shared" si="0"/>
         <v>TMOTNGSL1</v>
       </c>
-      <c r="C17" s="28" t="s">
+      <c r="C18" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D18" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="E17" s="28">
+      <c r="E18" s="28">
         <v>2022</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F18" s="29">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G17" s="28">
+      <c r="G18" s="28">
         <v>9</v>
       </c>
-      <c r="H17" s="28">
+      <c r="H18" s="28">
         <v>1.2</v>
       </c>
-      <c r="I17" s="28">
+      <c r="I18" s="28">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J17" s="29">
+      <c r="J18" s="29">
         <v>0.02</v>
       </c>
-      <c r="K17" s="28">
+      <c r="K18" s="28">
         <v>10</v>
       </c>
-      <c r="L17" s="45">
+      <c r="L18" s="45">
         <v>1E-3</v>
       </c>
-      <c r="N17" t="s">
+      <c r="N18" t="s">
         <v>62</v>
       </c>
-      <c r="P17" t="s">
+      <c r="P18" t="s">
         <v>107</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="Q18" t="s">
         <v>117</v>
       </c>
-      <c r="R17" t="s">
+      <c r="R18" t="s">
         <v>95</v>
       </c>
-      <c r="S17" t="s">
+      <c r="S18" t="s">
         <v>66</v>
       </c>
-      <c r="U17" t="s">
+      <c r="U18" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B18" t="str">
+    <row r="19" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B19" t="str">
         <f t="shared" si="0"/>
         <v>TTRINLPG1</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C19" t="s">
         <v>75</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D19" t="s">
         <v>101</v>
       </c>
-      <c r="E18">
+      <c r="E19">
         <v>2022</v>
       </c>
-      <c r="F18" s="18">
+      <c r="F19" s="18">
         <v>0.68</v>
       </c>
-      <c r="G18">
+      <c r="G19">
         <v>15</v>
       </c>
-      <c r="H18">
+      <c r="H19">
         <v>2</v>
       </c>
-      <c r="I18">
+      <c r="I19">
         <v>4</v>
       </c>
-      <c r="J18" s="18">
+      <c r="J19" s="18">
         <v>0.04</v>
       </c>
-      <c r="K18">
+      <c r="K19">
         <v>10</v>
       </c>
-      <c r="L18">
+      <c r="L19">
         <v>1E-3</v>
       </c>
-      <c r="N18" t="s">
+      <c r="N19" t="s">
         <v>62</v>
       </c>
-      <c r="P18" t="s">
+      <c r="P19" t="s">
         <v>108</v>
       </c>
-      <c r="Q18" t="s">
+      <c r="Q19" t="s">
         <v>116</v>
       </c>
-      <c r="R18" t="s">
+      <c r="R19" t="s">
         <v>95</v>
       </c>
-      <c r="S18" t="s">
+      <c r="S19" t="s">
         <v>66</v>
       </c>
-      <c r="U18" t="s">
+      <c r="U19" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="19" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B19" s="27" t="str">
+    <row r="20" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B20" s="27" t="str">
         <f t="shared" si="0"/>
         <v>TTRINGSL1</v>
       </c>
-      <c r="C19" s="27" t="s">
+      <c r="C20" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="D20" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="E19" s="27">
+      <c r="E20" s="27">
         <v>2022</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F20" s="30">
         <v>0.7</v>
       </c>
-      <c r="G19" s="27">
+      <c r="G20" s="27">
         <v>14</v>
       </c>
-      <c r="H19" s="27">
+      <c r="H20" s="27">
         <v>2</v>
       </c>
-      <c r="I19" s="27">
+      <c r="I20" s="27">
         <v>3.8</v>
       </c>
-      <c r="J19" s="30">
+      <c r="J20" s="30">
         <v>0.04</v>
       </c>
-      <c r="K19" s="27">
+      <c r="K20" s="27">
         <v>10</v>
       </c>
-      <c r="L19" s="27">
+      <c r="L20" s="27">
         <v>1E-3</v>
       </c>
-      <c r="N19" t="s">
+      <c r="N20" t="s">
         <v>62</v>
       </c>
-      <c r="P19" t="s">
+      <c r="P20" t="s">
         <v>109</v>
       </c>
-      <c r="Q19" t="s">
+      <c r="Q20" t="s">
         <v>117</v>
       </c>
-      <c r="R19" t="s">
+      <c r="R20" t="s">
         <v>95</v>
       </c>
-      <c r="S19" t="s">
+      <c r="S20" t="s">
         <v>66</v>
       </c>
-      <c r="U19" t="s">
+      <c r="U20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B20" t="str">
+    <row r="21" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B21" t="str">
         <f t="shared" si="0"/>
         <v>TFRENDSL1</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C21" t="s">
         <v>74</v>
       </c>
-      <c r="D20" s="41" t="s">
+      <c r="D21" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="E20">
+      <c r="E21">
         <v>2022</v>
       </c>
-      <c r="F20" s="18">
+      <c r="F21" s="18">
         <v>0.4</v>
       </c>
-      <c r="G20">
+      <c r="G21">
         <v>55</v>
       </c>
-      <c r="H20">
+      <c r="H21">
         <v>12</v>
       </c>
-      <c r="I20">
+      <c r="I21">
         <v>82</v>
       </c>
-      <c r="J20" s="18">
+      <c r="J21" s="18">
         <v>1.1499999999999999</v>
       </c>
-      <c r="K20">
+      <c r="K21">
         <v>30</v>
       </c>
-      <c r="L20" s="25">
+      <c r="L21" s="25">
         <v>1E-3</v>
       </c>
-      <c r="N20" t="s">
+      <c r="N21" t="s">
         <v>62</v>
       </c>
-      <c r="P20" t="s">
+      <c r="P21" t="s">
         <v>110</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="Q21" t="s">
         <v>115</v>
       </c>
-      <c r="R20" t="s">
+      <c r="R21" t="s">
         <v>95</v>
       </c>
-      <c r="S20" t="s">
+      <c r="S21" t="s">
         <v>66</v>
       </c>
-      <c r="U20" t="s">
+      <c r="U21" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B21" s="27" t="str">
+    <row r="22" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B22" s="27" t="str">
         <f t="shared" si="0"/>
         <v>TAVINKER1</v>
       </c>
-      <c r="C21" s="27" t="s">
+      <c r="C22" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="D21" s="41" t="s">
+      <c r="D22" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="E21" s="27">
+      <c r="E22" s="27">
         <v>2022</v>
       </c>
-      <c r="F21" s="27">
+      <c r="F22" s="27">
         <v>0.1</v>
       </c>
-      <c r="G21" s="27">
+      <c r="G22" s="27">
         <v>65</v>
       </c>
-      <c r="H21" s="27">
+      <c r="H22" s="27">
         <v>180</v>
       </c>
-      <c r="I21" s="27">
+      <c r="I22" s="27">
         <v>50000</v>
       </c>
-      <c r="J21" s="27">
+      <c r="J22" s="27">
         <v>70</v>
       </c>
-      <c r="K21" s="27">
+      <c r="K22" s="27">
         <v>30</v>
       </c>
-      <c r="L21" s="27">
+      <c r="L22" s="27">
         <v>1E-3</v>
       </c>
-      <c r="N21" s="27" t="s">
+      <c r="N22" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="O21" s="27"/>
-      <c r="P21" s="27" t="s">
+      <c r="O22" s="27"/>
+      <c r="P22" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="Q21" s="27" t="s">
+      <c r="Q22" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="R21" s="27" t="s">
+      <c r="R22" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="S21" s="27" t="s">
+      <c r="S22" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="T21" s="27"/>
-      <c r="U21" s="27" t="s">
+      <c r="T22" s="27"/>
+      <c r="U22" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="V21" s="27"/>
+      <c r="V22" s="27"/>
     </row>
-    <row r="22" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B22" t="str">
+    <row r="23" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B23" t="str">
         <f t="shared" si="0"/>
         <v>TRAINDSL1</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C23" t="s">
         <v>74</v>
       </c>
-      <c r="D22" s="44" t="s">
+      <c r="D23" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="E22">
+      <c r="E23">
         <v>2022</v>
       </c>
-      <c r="F22">
+      <c r="F23">
         <v>0.26</v>
       </c>
-      <c r="G22">
+      <c r="G23">
         <v>60</v>
       </c>
-      <c r="H22">
+      <c r="H23">
         <v>400</v>
       </c>
-      <c r="I22">
+      <c r="I23">
         <v>2100</v>
       </c>
-      <c r="J22">
+      <c r="J23">
         <v>30</v>
       </c>
-      <c r="K22">
+      <c r="K23">
         <v>30</v>
       </c>
-      <c r="L22" s="25">
+      <c r="L23" s="25">
         <v>1E-3</v>
       </c>
-      <c r="N22" t="s">
+      <c r="N23" t="s">
         <v>62</v>
       </c>
-      <c r="P22" t="s">
+      <c r="P23" t="s">
         <v>112</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="Q23" t="s">
         <v>115</v>
       </c>
-      <c r="R22" t="s">
+      <c r="R23" t="s">
         <v>95</v>
       </c>
-      <c r="S22" t="s">
+      <c r="S23" t="s">
         <v>66</v>
       </c>
-      <c r="U22" t="s">
+      <c r="U23" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B23" t="str">
+    <row r="24" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B24" t="str">
         <f t="shared" si="0"/>
         <v>TMARNDSL1</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C24" t="s">
         <v>74</v>
       </c>
-      <c r="D23" s="41" t="s">
+      <c r="D24" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="E23">
+      <c r="E24">
         <v>2022</v>
       </c>
-      <c r="F23">
+      <c r="F24">
         <v>0.32</v>
       </c>
-      <c r="G23">
+      <c r="G24">
         <v>70</v>
       </c>
-      <c r="H23">
+      <c r="H24">
         <v>1000</v>
       </c>
-      <c r="I23">
+      <c r="I24">
         <v>6000</v>
       </c>
-      <c r="J23">
+      <c r="J24">
         <v>88</v>
       </c>
-      <c r="K23">
+      <c r="K24">
         <v>30</v>
       </c>
-      <c r="L23">
+      <c r="L24">
         <v>1E-3</v>
       </c>
-      <c r="N23" t="s">
+      <c r="N24" t="s">
         <v>62</v>
       </c>
-      <c r="P23" t="s">
+      <c r="P24" t="s">
         <v>113</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="Q24" t="s">
         <v>115</v>
       </c>
-      <c r="R23" t="s">
+      <c r="R24" t="s">
         <v>95</v>
       </c>
-      <c r="S23" t="s">
+      <c r="S24" t="s">
         <v>66</v>
       </c>
-      <c r="U23" t="s">
+      <c r="U24" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="24" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B24" t="str">
+    <row r="25" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B25" t="str">
         <f t="shared" si="0"/>
         <v>TMARNGSL1</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C25" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="41" t="s">
+      <c r="D25" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="E24">
+      <c r="E25">
         <v>2022</v>
       </c>
-      <c r="F24">
+      <c r="F25">
         <v>0.25</v>
       </c>
-      <c r="G24">
+      <c r="G25">
         <v>60</v>
       </c>
-      <c r="H24">
+      <c r="H25">
         <v>800</v>
       </c>
-      <c r="I24">
+      <c r="I25">
         <v>5800</v>
       </c>
-      <c r="J24">
+      <c r="J25">
         <v>82</v>
       </c>
-      <c r="K24">
+      <c r="K25">
         <v>30</v>
       </c>
-      <c r="L24">
+      <c r="L25">
         <v>1E-3</v>
       </c>
-      <c r="N24" t="s">
+      <c r="N25" t="s">
         <v>62</v>
       </c>
-      <c r="P24" t="s">
+      <c r="P25" t="s">
         <v>114</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="Q25" t="s">
         <v>117</v>
       </c>
-      <c r="R24" t="s">
+      <c r="R25" t="s">
         <v>95</v>
       </c>
-      <c r="S24" t="s">
+      <c r="S25" t="s">
         <v>66</v>
       </c>
-      <c r="U24" t="s">
+      <c r="U25" t="s">
         <v>73</v>
       </c>
     </row>
@@ -3614,19 +3694,19 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="B2:AC2"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="12" width="9.109375" style="34"/>
+    <col min="2" max="12" width="9.140625" style="34"/>
     <col min="13" max="13" width="5" style="34" customWidth="1"/>
     <col min="14" max="15" width="2" style="34" bestFit="1" customWidth="1"/>
-    <col min="16" max="26" width="9.109375" style="34"/>
+    <col min="16" max="26" width="9.140625" style="34"/>
     <col min="27" max="27" width="2" style="34" customWidth="1"/>
-    <col min="28" max="28" width="2.33203125" style="34" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.109375" style="34"/>
+    <col min="28" max="28" width="2.28515625" style="34" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="34"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B2" s="35" t="s">
         <v>84</v>
       </c>
